--- a/docs/urbn-copy-audit.xlsx
+++ b/docs/urbn-copy-audit.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -74,6 +74,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -151,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -198,6 +201,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -712,7 +721,7 @@
       </c>
       <c r="J6" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2069,7 @@
       </c>
       <c r="J34" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2166,7 @@
       </c>
       <c r="J36" s="19" t="inlineStr">
         <is>
-          <t>Applied. Note: the desktop hero artwork still contains a 'Don't pay before you verify' billboard: needs a new design asset.</t>
+          <t>Applied. Note: the desktop hero artwork still contains a 'Don't pay before you verify' billboard: needs a new design asset. Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2214,7 @@
       </c>
       <c r="J37" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2312,7 @@
       </c>
       <c r="J39" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2360,7 @@
       </c>
       <c r="J40" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2456,7 @@
       </c>
       <c r="J42" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2554,7 @@
       </c>
       <c r="J44" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3139,7 @@
       </c>
       <c r="J56" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3188,7 @@
       </c>
       <c r="J57" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3385,7 @@
       </c>
       <c r="J61" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3433,7 @@
       </c>
       <c r="J62" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3629,7 @@
       </c>
       <c r="J66" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3677,7 @@
       </c>
       <c r="J67" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3726,7 @@
       </c>
       <c r="J68" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5883,7 @@
       </c>
       <c r="J112" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5931,7 @@
       </c>
       <c r="J113" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -5970,7 +5979,7 @@
       </c>
       <c r="J114" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6027,7 @@
       </c>
       <c r="J115" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6123,7 @@
       </c>
       <c r="J117" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6270,7 @@
       </c>
       <c r="J120" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6318,7 @@
       </c>
       <c r="J121" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6368,7 @@
       </c>
       <c r="J122" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6465,7 @@
       </c>
       <c r="J124" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6565,7 @@
       </c>
       <c r="J126" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7348,7 @@
       </c>
       <c r="J142" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -7388,7 +7397,7 @@
       </c>
       <c r="J143" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7447,7 @@
       </c>
       <c r="J144" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7593,7 @@
       </c>
       <c r="J147" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7642,7 @@
       </c>
       <c r="J148" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7888,7 @@
       </c>
       <c r="J153" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8084,7 @@
       </c>
       <c r="J157" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8972,7 @@
       </c>
       <c r="J175" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9117,7 @@
       </c>
       <c r="J178" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9167,7 @@
       </c>
       <c r="J179" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9415,7 @@
       </c>
       <c r="J184" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9467,7 @@
       </c>
       <c r="J185" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9713,7 @@
       </c>
       <c r="J190" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10497,7 @@
       </c>
       <c r="J206" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10548,7 @@
       </c>
       <c r="J207" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -10735,7 +10744,7 @@
       </c>
       <c r="J211" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10891,7 @@
       </c>
       <c r="J214" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -11126,7 +11135,7 @@
       </c>
       <c r="J219" s="18" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Applied Then adjusted for property scope (see Tone rules: home / property / space / places).</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12415,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -14096,7 +14104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="110" customWidth="1" style="16" min="1" max="1"/>
@@ -14177,6 +14185,48 @@
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>• Rating key: 9–10 keep · 7–8 polish · 5–6 rewrite · 1–4 replace or remove.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Positioning: keep 'The digital infrastructure for housing' as the brand line, but supporting copy shows the full scope (homes, shops, offices, schools, clinics and other property activities).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>• Home: residential searches and renter-specific copy (e.g. 'For Renters &amp; Home Seekers', 'Browse Homes' on the renters page).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>• Property: DPI, verification, ownership, management and general listings (e.g. 'Find the Right Property for You.').</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>• Space: units or different uses within a building (e.g. a flat, a shop or an office suite).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>• Places and activities: Nearby discovery (e.g. 'Discover What's Around You.').</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>• 'Property activities' (the app's term), not 'housing activities'.</t>
         </is>
       </c>
     </row>
